--- a/output_excel/5232486.xlsx
+++ b/output_excel/5232486.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>C12X1000112,5KVA2,CE3112,5KVASMFL112,5KVAIP | 3 1RU6A (DCIM) 112,5KVA *DEIXAR *GIRAR ESTR. JUMPER PRIMÁRIA* | 2 7 | C12X600112,5KVASMFL 2,CE3 | ABERTO* | ETAPA PONTO 2 104 | RCAL70 P1-11</t>
+          <t>C12X1000112,5KVA2 CE3112,5KVASMFL112,5KVAIP | 3 1RU6A (DCIM) 112,5KVA *DEIXAR *GIRAR ESTR. JUMPER PRIMÁRIA* | 2 7 | C12X600112,5KVASMFL 2 CE3 | ABERTO* | ETAPA PONTO 2 104 | RCAL70 P1-11</t>
         </is>
       </c>
       <c r="L3" s="3" t="n">
